--- a/ig/DM-MARS-2026/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="3207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="3255">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202602240000</t>
+    <t>202603110000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T15:40:47-00:00</t>
+    <t>2026-03-11T14:52:01-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2623,6 +2623,60 @@
     <t>Fréquentation d'une collectivité accueillant des sujets à risque de rougeole grave</t>
   </si>
   <si>
+    <t>GEN-422</t>
+  </si>
+  <si>
+    <t>Le patient a signé un consentement à la transmission de ses données au(x) registre(s) de l'ERN GloBE-Reg</t>
+  </si>
+  <si>
+    <t>GEN-423</t>
+  </si>
+  <si>
+    <t>Présence de sujet à risque de rougeole grave dans l’entourage du cas (femme enceinte, immunodéprimé, nourrisson)</t>
+  </si>
+  <si>
+    <t>GEN-424</t>
+  </si>
+  <si>
+    <t>Administration d’immunoglobulines aux contacts à risque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-425</t>
+  </si>
+  <si>
+    <t>Nombre d'admministration d'immunoglobines aux contacts àrisque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-426</t>
+  </si>
+  <si>
+    <t>Administration dans les 72 heures suivant le 1er contact du vaccin ROR aux personnes contact</t>
+  </si>
+  <si>
+    <t>GEN-427</t>
+  </si>
+  <si>
+    <t>Nombre d'administration dans les 72 heures suivant le 1er contact du vaccin ROR aux personnes contact</t>
+  </si>
+  <si>
+    <t>GEN-428</t>
+  </si>
+  <si>
+    <t>Souhaitez-vous recevoir des kits pour prélèvements et envois d’échantillons de salive au CNR (recherche d’IgM/PCR) ?</t>
+  </si>
+  <si>
+    <t>GEN-429</t>
+  </si>
+  <si>
+    <t>Nombre de kits</t>
+  </si>
+  <si>
+    <t>GEN-430</t>
+  </si>
+  <si>
+    <t>Séjour à l’étranger pour les autres cas de rougeole dans l'entourage</t>
+  </si>
+  <si>
     <t>MED-001</t>
   </si>
   <si>
@@ -8449,6 +8503,66 @@
     <t>Complication</t>
   </si>
   <si>
+    <t>MED-1340</t>
+  </si>
+  <si>
+    <t>Vaccination autre flavivirus</t>
+  </si>
+  <si>
+    <t>MED-1341</t>
+  </si>
+  <si>
+    <t>Autre(s) exposition(s)</t>
+  </si>
+  <si>
+    <t>MED-1342</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 60-65 ans</t>
+  </si>
+  <si>
+    <t>MED-1343</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 66-69 ans</t>
+  </si>
+  <si>
+    <t>MED-1344</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1345</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 76 ans et plus</t>
+  </si>
+  <si>
+    <t>MED-1346</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 18-25 ans</t>
+  </si>
+  <si>
+    <t>MED-1347</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 45-50 ans</t>
+  </si>
+  <si>
+    <t>MED-1348</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 60-65 ans</t>
+  </si>
+  <si>
+    <t>MED-1349</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
     <t>ORG-001</t>
   </si>
   <si>
@@ -9323,6 +9437,36 @@
   </si>
   <si>
     <t>Intervenant à domicile</t>
+  </si>
+  <si>
+    <t>ORG-225</t>
+  </si>
+  <si>
+    <t>RCP Métastase osseuse</t>
+  </si>
+  <si>
+    <t>ORG-226</t>
+  </si>
+  <si>
+    <t>RCP Cancers rares</t>
+  </si>
+  <si>
+    <t>ORG-227</t>
+  </si>
+  <si>
+    <t>Domicile ou milieu ordinaire</t>
+  </si>
+  <si>
+    <t>ORG-228</t>
+  </si>
+  <si>
+    <t>Etablissement médico-social</t>
+  </si>
+  <si>
+    <t>ORG-229</t>
+  </si>
+  <si>
+    <t>Provenance inconnue</t>
   </si>
   <si>
     <t>PAT-001</t>
@@ -10036,7 +10180,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1582"/>
+  <dimension ref="A1:D1606"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16553,7 +16697,7 @@
         <v>1137</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>200</v>
+        <v>1138</v>
       </c>
       <c r="D543" s="2"/>
     </row>
@@ -16562,10 +16706,10 @@
         <v>57</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D544" s="2"/>
     </row>
@@ -16574,10 +16718,10 @@
         <v>57</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D545" s="2"/>
     </row>
@@ -16586,10 +16730,10 @@
         <v>57</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -16598,10 +16742,10 @@
         <v>57</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D547" s="2"/>
     </row>
@@ -16610,10 +16754,10 @@
         <v>57</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -16622,10 +16766,10 @@
         <v>57</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -16634,10 +16778,10 @@
         <v>57</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D550" s="2"/>
     </row>
@@ -16646,10 +16790,10 @@
         <v>57</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -16658,10 +16802,10 @@
         <v>57</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1155</v>
+        <v>200</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -21185,7 +21329,7 @@
         <v>1908</v>
       </c>
       <c r="C929" t="s" s="2">
-        <v>569</v>
+        <v>1909</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -21194,10 +21338,10 @@
         <v>57</v>
       </c>
       <c r="B930" t="s" s="2">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C930" t="s" s="2">
-        <v>571</v>
+        <v>1911</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -21206,10 +21350,10 @@
         <v>57</v>
       </c>
       <c r="B931" t="s" s="2">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="C931" t="s" s="2">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -21218,10 +21362,10 @@
         <v>57</v>
       </c>
       <c r="B932" t="s" s="2">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="C932" t="s" s="2">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -21230,10 +21374,10 @@
         <v>57</v>
       </c>
       <c r="B933" t="s" s="2">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="C933" t="s" s="2">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -21242,10 +21386,10 @@
         <v>57</v>
       </c>
       <c r="B934" t="s" s="2">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="C934" t="s" s="2">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -21254,10 +21398,10 @@
         <v>57</v>
       </c>
       <c r="B935" t="s" s="2">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C935" t="s" s="2">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -21266,10 +21410,10 @@
         <v>57</v>
       </c>
       <c r="B936" t="s" s="2">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="C936" t="s" s="2">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -21278,10 +21422,10 @@
         <v>57</v>
       </c>
       <c r="B937" t="s" s="2">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="C937" t="s" s="2">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -21290,10 +21434,10 @@
         <v>57</v>
       </c>
       <c r="B938" t="s" s="2">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="C938" t="s" s="2">
-        <v>1925</v>
+        <v>569</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -21302,10 +21446,10 @@
         <v>57</v>
       </c>
       <c r="B939" t="s" s="2">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C939" t="s" s="2">
-        <v>1927</v>
+        <v>571</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -21725,7 +21869,7 @@
         <v>1996</v>
       </c>
       <c r="C974" t="s" s="2">
-        <v>1951</v>
+        <v>1997</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -21734,10 +21878,10 @@
         <v>57</v>
       </c>
       <c r="B975" t="s" s="2">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C975" t="s" s="2">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -21746,10 +21890,10 @@
         <v>57</v>
       </c>
       <c r="B976" t="s" s="2">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C976" t="s" s="2">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -21758,10 +21902,10 @@
         <v>57</v>
       </c>
       <c r="B977" t="s" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C977" t="s" s="2">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -21770,10 +21914,10 @@
         <v>57</v>
       </c>
       <c r="B978" t="s" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C978" t="s" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -21782,10 +21926,10 @@
         <v>57</v>
       </c>
       <c r="B979" t="s" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C979" t="s" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -21794,10 +21938,10 @@
         <v>57</v>
       </c>
       <c r="B980" t="s" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C980" t="s" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -21806,10 +21950,10 @@
         <v>57</v>
       </c>
       <c r="B981" t="s" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C981" t="s" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -21818,10 +21962,10 @@
         <v>57</v>
       </c>
       <c r="B982" t="s" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C982" t="s" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -21830,10 +21974,10 @@
         <v>57</v>
       </c>
       <c r="B983" t="s" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C983" t="s" s="2">
-        <v>2014</v>
+        <v>1969</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -23297,7 +23441,7 @@
         <v>2257</v>
       </c>
       <c r="C1105" t="s" s="2">
-        <v>2206</v>
+        <v>2258</v>
       </c>
       <c r="D1105" s="2"/>
     </row>
@@ -23306,10 +23450,10 @@
         <v>57</v>
       </c>
       <c r="B1106" t="s" s="2">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="C1106" t="s" s="2">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="D1106" s="2"/>
     </row>
@@ -23318,10 +23462,10 @@
         <v>57</v>
       </c>
       <c r="B1107" t="s" s="2">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="C1107" t="s" s="2">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="D1107" s="2"/>
     </row>
@@ -23330,10 +23474,10 @@
         <v>57</v>
       </c>
       <c r="B1108" t="s" s="2">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="C1108" t="s" s="2">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="D1108" s="2"/>
     </row>
@@ -23342,10 +23486,10 @@
         <v>57</v>
       </c>
       <c r="B1109" t="s" s="2">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C1109" t="s" s="2">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="D1109" s="2"/>
     </row>
@@ -23354,10 +23498,10 @@
         <v>57</v>
       </c>
       <c r="B1110" t="s" s="2">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="C1110" t="s" s="2">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="D1110" s="2"/>
     </row>
@@ -23366,10 +23510,10 @@
         <v>57</v>
       </c>
       <c r="B1111" t="s" s="2">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C1111" t="s" s="2">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="D1111" s="2"/>
     </row>
@@ -23378,10 +23522,10 @@
         <v>57</v>
       </c>
       <c r="B1112" t="s" s="2">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C1112" t="s" s="2">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="D1112" s="2"/>
     </row>
@@ -23390,10 +23534,10 @@
         <v>57</v>
       </c>
       <c r="B1113" t="s" s="2">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C1113" t="s" s="2">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="D1113" s="2"/>
     </row>
@@ -23402,10 +23546,10 @@
         <v>57</v>
       </c>
       <c r="B1114" t="s" s="2">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="C1114" t="s" s="2">
-        <v>2275</v>
+        <v>2224</v>
       </c>
       <c r="D1114" s="2"/>
     </row>
@@ -25577,7 +25721,7 @@
         <v>2636</v>
       </c>
       <c r="C1295" t="s" s="2">
-        <v>2589</v>
+        <v>2637</v>
       </c>
       <c r="D1295" s="2"/>
     </row>
@@ -25586,10 +25730,10 @@
         <v>57</v>
       </c>
       <c r="B1296" t="s" s="2">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="C1296" t="s" s="2">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="D1296" s="2"/>
     </row>
@@ -25598,10 +25742,10 @@
         <v>57</v>
       </c>
       <c r="B1297" t="s" s="2">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="C1297" t="s" s="2">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="D1297" s="2"/>
     </row>
@@ -25610,10 +25754,10 @@
         <v>57</v>
       </c>
       <c r="B1298" t="s" s="2">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="C1298" t="s" s="2">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="D1298" s="2"/>
     </row>
@@ -25622,10 +25766,10 @@
         <v>57</v>
       </c>
       <c r="B1299" t="s" s="2">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="C1299" t="s" s="2">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="D1299" s="2"/>
     </row>
@@ -25634,10 +25778,10 @@
         <v>57</v>
       </c>
       <c r="B1300" t="s" s="2">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="C1300" t="s" s="2">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="D1300" s="2"/>
     </row>
@@ -25646,10 +25790,10 @@
         <v>57</v>
       </c>
       <c r="B1301" t="s" s="2">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="C1301" t="s" s="2">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="D1301" s="2"/>
     </row>
@@ -25658,10 +25802,10 @@
         <v>57</v>
       </c>
       <c r="B1302" t="s" s="2">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="C1302" t="s" s="2">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="D1302" s="2"/>
     </row>
@@ -25670,10 +25814,10 @@
         <v>57</v>
       </c>
       <c r="B1303" t="s" s="2">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="C1303" t="s" s="2">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="D1303" s="2"/>
     </row>
@@ -25682,10 +25826,10 @@
         <v>57</v>
       </c>
       <c r="B1304" t="s" s="2">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="C1304" t="s" s="2">
-        <v>2654</v>
+        <v>2607</v>
       </c>
       <c r="D1304" s="2"/>
     </row>
@@ -26033,7 +26177,7 @@
         <v>2711</v>
       </c>
       <c r="C1333" t="s" s="2">
-        <v>300</v>
+        <v>2712</v>
       </c>
       <c r="D1333" s="2"/>
     </row>
@@ -26042,10 +26186,10 @@
         <v>57</v>
       </c>
       <c r="B1334" t="s" s="2">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="C1334" t="s" s="2">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="D1334" s="2"/>
     </row>
@@ -26054,10 +26198,10 @@
         <v>57</v>
       </c>
       <c r="B1335" t="s" s="2">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="C1335" t="s" s="2">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="D1335" s="2"/>
     </row>
@@ -26066,10 +26210,10 @@
         <v>57</v>
       </c>
       <c r="B1336" t="s" s="2">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="C1336" t="s" s="2">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="D1336" s="2"/>
     </row>
@@ -26078,10 +26222,10 @@
         <v>57</v>
       </c>
       <c r="B1337" t="s" s="2">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="C1337" t="s" s="2">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D1337" s="2"/>
     </row>
@@ -26090,10 +26234,10 @@
         <v>57</v>
       </c>
       <c r="B1338" t="s" s="2">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="C1338" t="s" s="2">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="D1338" s="2"/>
     </row>
@@ -26102,10 +26246,10 @@
         <v>57</v>
       </c>
       <c r="B1339" t="s" s="2">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="C1339" t="s" s="2">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="D1339" s="2"/>
     </row>
@@ -26114,10 +26258,10 @@
         <v>57</v>
       </c>
       <c r="B1340" t="s" s="2">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="C1340" t="s" s="2">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="D1340" s="2"/>
     </row>
@@ -26126,10 +26270,10 @@
         <v>57</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="C1341" t="s" s="2">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="D1341" s="2"/>
     </row>
@@ -26138,10 +26282,10 @@
         <v>57</v>
       </c>
       <c r="B1342" t="s" s="2">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="C1342" t="s" s="2">
-        <v>2729</v>
+        <v>300</v>
       </c>
       <c r="D1342" s="2"/>
     </row>
@@ -26189,7 +26333,7 @@
         <v>2736</v>
       </c>
       <c r="C1346" t="s" s="2">
-        <v>59</v>
+        <v>2737</v>
       </c>
       <c r="D1346" s="2"/>
     </row>
@@ -26198,10 +26342,10 @@
         <v>57</v>
       </c>
       <c r="B1347" t="s" s="2">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="C1347" t="s" s="2">
-        <v>61</v>
+        <v>2739</v>
       </c>
       <c r="D1347" s="2"/>
     </row>
@@ -26210,10 +26354,10 @@
         <v>57</v>
       </c>
       <c r="B1348" t="s" s="2">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="C1348" t="s" s="2">
-        <v>63</v>
+        <v>2741</v>
       </c>
       <c r="D1348" s="2"/>
     </row>
@@ -26222,10 +26366,10 @@
         <v>57</v>
       </c>
       <c r="B1349" t="s" s="2">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C1349" t="s" s="2">
-        <v>2740</v>
+        <v>2743</v>
       </c>
       <c r="D1349" s="2"/>
     </row>
@@ -26234,10 +26378,10 @@
         <v>57</v>
       </c>
       <c r="B1350" t="s" s="2">
-        <v>2741</v>
+        <v>2744</v>
       </c>
       <c r="C1350" t="s" s="2">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D1350" s="2"/>
     </row>
@@ -26246,10 +26390,10 @@
         <v>57</v>
       </c>
       <c r="B1351" t="s" s="2">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="C1351" t="s" s="2">
-        <v>2744</v>
+        <v>2747</v>
       </c>
       <c r="D1351" s="2"/>
     </row>
@@ -26258,10 +26402,10 @@
         <v>57</v>
       </c>
       <c r="B1352" t="s" s="2">
-        <v>2745</v>
+        <v>2748</v>
       </c>
       <c r="C1352" t="s" s="2">
-        <v>2746</v>
+        <v>2749</v>
       </c>
       <c r="D1352" s="2"/>
     </row>
@@ -26270,10 +26414,10 @@
         <v>57</v>
       </c>
       <c r="B1353" t="s" s="2">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="C1353" t="s" s="2">
-        <v>2748</v>
+        <v>2751</v>
       </c>
       <c r="D1353" s="2"/>
     </row>
@@ -26282,10 +26426,10 @@
         <v>57</v>
       </c>
       <c r="B1354" t="s" s="2">
-        <v>2749</v>
+        <v>2752</v>
       </c>
       <c r="C1354" t="s" s="2">
-        <v>2750</v>
+        <v>2753</v>
       </c>
       <c r="D1354" s="2"/>
     </row>
@@ -26294,10 +26438,10 @@
         <v>57</v>
       </c>
       <c r="B1355" t="s" s="2">
-        <v>2751</v>
+        <v>2754</v>
       </c>
       <c r="C1355" t="s" s="2">
-        <v>2752</v>
+        <v>59</v>
       </c>
       <c r="D1355" s="2"/>
     </row>
@@ -26306,10 +26450,10 @@
         <v>57</v>
       </c>
       <c r="B1356" t="s" s="2">
-        <v>2753</v>
+        <v>2755</v>
       </c>
       <c r="C1356" t="s" s="2">
-        <v>2754</v>
+        <v>61</v>
       </c>
       <c r="D1356" s="2"/>
     </row>
@@ -26318,10 +26462,10 @@
         <v>57</v>
       </c>
       <c r="B1357" t="s" s="2">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="C1357" t="s" s="2">
-        <v>2756</v>
+        <v>63</v>
       </c>
       <c r="D1357" s="2"/>
     </row>
@@ -29024,6 +29168,294 @@
         <v>3206</v>
       </c>
       <c r="D1582" s="2"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1583" t="s" s="2">
+        <v>3207</v>
+      </c>
+      <c r="C1583" t="s" s="2">
+        <v>3208</v>
+      </c>
+      <c r="D1583" s="2"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1584" t="s" s="2">
+        <v>3209</v>
+      </c>
+      <c r="C1584" t="s" s="2">
+        <v>3210</v>
+      </c>
+      <c r="D1584" s="2"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1585" t="s" s="2">
+        <v>3211</v>
+      </c>
+      <c r="C1585" t="s" s="2">
+        <v>3212</v>
+      </c>
+      <c r="D1585" s="2"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1586" t="s" s="2">
+        <v>3213</v>
+      </c>
+      <c r="C1586" t="s" s="2">
+        <v>3214</v>
+      </c>
+      <c r="D1586" s="2"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1587" t="s" s="2">
+        <v>3215</v>
+      </c>
+      <c r="C1587" t="s" s="2">
+        <v>3216</v>
+      </c>
+      <c r="D1587" s="2"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1588" t="s" s="2">
+        <v>3217</v>
+      </c>
+      <c r="C1588" t="s" s="2">
+        <v>3218</v>
+      </c>
+      <c r="D1588" s="2"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1589" t="s" s="2">
+        <v>3219</v>
+      </c>
+      <c r="C1589" t="s" s="2">
+        <v>3220</v>
+      </c>
+      <c r="D1589" s="2"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1590" t="s" s="2">
+        <v>3221</v>
+      </c>
+      <c r="C1590" t="s" s="2">
+        <v>3222</v>
+      </c>
+      <c r="D1590" s="2"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1591" t="s" s="2">
+        <v>3223</v>
+      </c>
+      <c r="C1591" t="s" s="2">
+        <v>3224</v>
+      </c>
+      <c r="D1591" s="2"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1592" t="s" s="2">
+        <v>3225</v>
+      </c>
+      <c r="C1592" t="s" s="2">
+        <v>3226</v>
+      </c>
+      <c r="D1592" s="2"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1593" t="s" s="2">
+        <v>3227</v>
+      </c>
+      <c r="C1593" t="s" s="2">
+        <v>3228</v>
+      </c>
+      <c r="D1593" s="2"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1594" t="s" s="2">
+        <v>3229</v>
+      </c>
+      <c r="C1594" t="s" s="2">
+        <v>3230</v>
+      </c>
+      <c r="D1594" s="2"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1595" t="s" s="2">
+        <v>3231</v>
+      </c>
+      <c r="C1595" t="s" s="2">
+        <v>3232</v>
+      </c>
+      <c r="D1595" s="2"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1596" t="s" s="2">
+        <v>3233</v>
+      </c>
+      <c r="C1596" t="s" s="2">
+        <v>3234</v>
+      </c>
+      <c r="D1596" s="2"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1597" t="s" s="2">
+        <v>3235</v>
+      </c>
+      <c r="C1597" t="s" s="2">
+        <v>3236</v>
+      </c>
+      <c r="D1597" s="2"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1598" t="s" s="2">
+        <v>3237</v>
+      </c>
+      <c r="C1598" t="s" s="2">
+        <v>3238</v>
+      </c>
+      <c r="D1598" s="2"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1599" t="s" s="2">
+        <v>3239</v>
+      </c>
+      <c r="C1599" t="s" s="2">
+        <v>3240</v>
+      </c>
+      <c r="D1599" s="2"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1600" t="s" s="2">
+        <v>3241</v>
+      </c>
+      <c r="C1600" t="s" s="2">
+        <v>3242</v>
+      </c>
+      <c r="D1600" s="2"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1601" t="s" s="2">
+        <v>3243</v>
+      </c>
+      <c r="C1601" t="s" s="2">
+        <v>3244</v>
+      </c>
+      <c r="D1601" s="2"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1602" t="s" s="2">
+        <v>3245</v>
+      </c>
+      <c r="C1602" t="s" s="2">
+        <v>3246</v>
+      </c>
+      <c r="D1602" s="2"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1603" t="s" s="2">
+        <v>3247</v>
+      </c>
+      <c r="C1603" t="s" s="2">
+        <v>3248</v>
+      </c>
+      <c r="D1603" s="2"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1604" t="s" s="2">
+        <v>3249</v>
+      </c>
+      <c r="C1604" t="s" s="2">
+        <v>3250</v>
+      </c>
+      <c r="D1604" s="2"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1605" t="s" s="2">
+        <v>3251</v>
+      </c>
+      <c r="C1605" t="s" s="2">
+        <v>3252</v>
+      </c>
+      <c r="D1605" s="2"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1606" t="s" s="2">
+        <v>3253</v>
+      </c>
+      <c r="C1606" t="s" s="2">
+        <v>3254</v>
+      </c>
+      <c r="D1606" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM-MARS-2026/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="3255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="3257">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202603110000</t>
+    <t>202604200000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:52:01-00:00</t>
+    <t>2026-04-20T11:06:51-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8561,6 +8561,12 @@
   </si>
   <si>
     <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1350</t>
+  </si>
+  <si>
+    <t>Entrées/sorties hydro-électrolytiques</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10180,7 +10186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1606"/>
+  <dimension ref="A1:D1607"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29457,6 +29463,18 @@
       </c>
       <c r="D1606" s="2"/>
     </row>
+    <row r="1607">
+      <c r="A1607" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1607" t="s" s="2">
+        <v>3255</v>
+      </c>
+      <c r="C1607" t="s" s="2">
+        <v>3256</v>
+      </c>
+      <c r="D1607" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
